--- a/artfynd/A 59891-2024 artfynd.xlsx
+++ b/artfynd/A 59891-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4222804</v>
+        <v>148672</v>
       </c>
       <c r="B2" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>522</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sjötåtel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Deschampsia setacea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huds.) Hack.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Raslången Ola-Jeppsön, Bl</t>
+          <t>Ola Jeppsöns SV sida, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464843.5539526381</v>
+        <v>464845</v>
       </c>
       <c r="R2" t="n">
-        <v>6234547.802912715</v>
+        <v>6234551</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +738,24 @@
           <t>Jämshög</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>K-Olo-0010</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Koordinat: 3E7c2148, enstaka tuvor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,35 +767,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Nilsson</t>
+          <t>K-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66939884</v>
+        <v>16457814</v>
       </c>
       <c r="B3" t="n">
-        <v>97636</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,22 +824,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ola Jeppsöns SV sida, Bl</t>
+          <t>Ola Jeppsöns sydöstra sida, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464844.6945194842</v>
+        <v>464863</v>
       </c>
       <c r="R3" t="n">
-        <v>6234551.126187163</v>
+        <v>6234486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,27 +860,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>K-Olo-0010</t>
+          <t>K-Olo-0239</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>små tuvor med vippor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,22 +887,254 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>oligotrof sjö</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Ivar Björegren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66959510</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100475</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>522</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sjötåtel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Deschampsia setacea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Huds.) Hack.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ola Jeppsön, N delen, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465056</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6234744</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Olofström</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jämshög</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>K-Olo-0370</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-07-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-07-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ivar Björegren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4222804</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Raslången Ola-Jeppsön, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>464844</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6234548</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Olofström</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jämshög</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-09-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59891-2024 artfynd.xlsx
+++ b/artfynd/A 59891-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/148672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16457814</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66959510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,8 +1155,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4222804</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>